--- a/server/templates/template - Copy.xlsx
+++ b/server/templates/template - Copy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11580" tabRatio="789" activeTab="7"/>
+    <workbookView windowWidth="27945" windowHeight="12300" tabRatio="789" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="スタート" sheetId="9" r:id="rId1"/>
@@ -7203,7 +7203,7 @@
                   <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{d61f265c-7b2a-4edc-b10c-f8a864c1cf56}" type="VALUE">
+                    <a:fld id="{a0d40c82-19a1-4cda-b48f-ecb848befc6f}" type="VALUE">
                       <a:t>[VALUE]</a:t>
                     </a:fld>
                     <a:endParaRPr b="0" i="0" u="none" strike="noStrike" baseline="0">
@@ -8091,7 +8091,7 @@
                   <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7ec7cadf-7300-459e-a9ad-407de07cf0bf}" type="VALUE">
+                    <a:fld id="{721766e6-b579-49f7-b271-c687fc72a0ee}" type="VALUE">
                       <a:t>[VALUE]</a:t>
                     </a:fld>
                     <a:endParaRPr b="0" i="0" u="none" strike="noStrike" baseline="0">
@@ -28133,7 +28133,6 @@
       <c r="R32" s="11"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="XkYp19lYupFIzhFC5BaWwI82sHmMfkLmROZ9N8BZCpLWfZ+cJHHgfptDIgx5U6Q9BxQCCls/zFaF0OpSU+u7fQ==" saltValue="64KF9LLHOXSyjYGvCpyw5g==" spinCount="100000" sheet="1" objects="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="N2:P2"/>
